--- a/evaluation_forms/005_employee_overall_satisfaction_survey_form--evaluation_forms.xlsx
+++ b/evaluation_forms/005_employee_overall_satisfaction_survey_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Overall Happiness</t>
+          <t>Overall Happiness 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mission Understanding</t>
+          <t>Mission Understanding 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,11 +640,287 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Recommend Company</t>
+          <t>Recommend Company 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>work_life_balance</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Work-Life Balance</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>feedback_from_manager</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Feedback from Manager</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>growth_opportunities</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Growth Opportunities</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>feedback_importance</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Feedback Importance</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>communication</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>growth_opportunities_2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Growth Opportunities 2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>report_issues</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Report Issues</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>empowered_to_own_work</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Empowered to Own Work</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>overall_satisfaction</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Overall Satisfaction</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>communication_2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Communication 2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>support_growth</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Support for Growth</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>support_growth_2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Support Growth 2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -661,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>very likely</t>
         </is>
       </c>
     </row>
@@ -711,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>somewhat likely</t>
         </is>
       </c>
     </row>
@@ -728,29 +1004,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>not likely</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>recommend_company_2_choices</t>
+          <t>recommend_company_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>not at all</t>
         </is>
       </c>
     </row>
@@ -762,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>very likely</t>
         </is>
       </c>
     </row>
@@ -779,12 +1055,386 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>somewhat likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>recommend_company_2_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>not_likely</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>not likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>recommend_company_2_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>not_at_all</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>not at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>feedback_from_manager_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>often</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>often</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>feedback_from_manager_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>feedback_from_manager_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>growth_opportunities_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>strongly_agree</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>strongly agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>growth_opportunities_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>somewhat_agree</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>somewhat agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>growth_opportunities_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>growth_opportunities_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>somewhat_disagree</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>somewhat disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>growth_opportunities_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>strongly_disagree</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>strongly disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>growth_opportunities_2_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>strongly_agree</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>strongly agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>growth_opportunities_2_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>somewhat_agree</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>somewhat agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>growth_opportunities_2_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>growth_opportunities_2_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>somewhat_disagree</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>somewhat disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>growth_opportunities_2_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>strongly_disagree</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>strongly disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>report_issues_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>very_likely</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>very likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>report_issues_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>somewhat_likely</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>somewhat likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>report_issues_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>not_likely</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>not likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>report_issues_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>not_at_all</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>not at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>empowered_to_own_work_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>often</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>often</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>empowered_to_own_work_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>empowered_to_own_work_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>rarely</t>
         </is>
       </c>
     </row>
